--- a/Single_input_library/Single_input_Sublib_Indis.xlsx
+++ b/Single_input_library/Single_input_Sublib_Indis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr checkCompatibility="1" autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rice\Thesis\Bashor Lab\Data\2024.05.11 - 166k Sub Libraries Fine Tuning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethanwong/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EDDAFB-BA17-4979-9EEF-B606846B0D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED8AD9A-F6E7-9742-B2BC-811E4F032656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="600" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FCS Express Report" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="52">
   <si>
     <t>GEO MEAN (GFP)</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t>MAEs</t>
-  </si>
-  <si>
-    <t>39 - fucked</t>
   </si>
   <si>
     <t>ML Predictions</t>
@@ -520,6 +517,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -530,15 +536,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -846,82 +843,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" style="1"/>
-    <col min="19" max="19" width="6.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5" style="1"/>
+    <col min="19" max="19" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.5" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="1"/>
-    <col min="31" max="31" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.5" style="1"/>
+    <col min="31" max="31" width="7.5" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.44140625" style="1"/>
-    <col min="35" max="35" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.5" style="1"/>
+    <col min="35" max="35" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="11.44140625" style="1"/>
+    <col min="38" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="C1" s="49" t="s">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.15">
+      <c r="C1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="49" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="51"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="53"/>
+      <c r="H1" s="54"/>
       <c r="I1" s="6"/>
-      <c r="L1" s="52" t="s">
+      <c r="L1" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
       <c r="Q1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="AE1" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="51"/>
-      <c r="AI1" s="49" t="s">
+      <c r="AE1" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="54"/>
+      <c r="AI1" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="51"/>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="54"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1023,7 +1020,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>31</v>
       </c>
@@ -1110,14 +1107,14 @@
       <c r="AF3" s="30">
         <v>110079.77</v>
       </c>
-      <c r="AG3" s="53">
+      <c r="AG3" s="49">
         <v>1.1832142000000001</v>
       </c>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="30"/>
       <c r="AK3" s="9"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>32</v>
       </c>
@@ -1204,14 +1201,14 @@
       <c r="AF4" s="30">
         <v>445.12166999999999</v>
       </c>
-      <c r="AG4" s="53">
+      <c r="AG4" s="49">
         <v>0.60975354999999998</v>
       </c>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="30"/>
       <c r="AK4" s="9"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
         <v>33</v>
       </c>
@@ -1298,14 +1295,14 @@
       <c r="AF5" s="30">
         <v>85940.883000000002</v>
       </c>
-      <c r="AG5" s="53">
+      <c r="AG5" s="49">
         <v>47.967896000000003</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="30"/>
       <c r="AK5" s="9"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
         <v>34</v>
       </c>
@@ -1392,14 +1389,14 @@
       <c r="AF6" s="30">
         <v>134489.64000000001</v>
       </c>
-      <c r="AG6" s="53">
+      <c r="AG6" s="49">
         <v>50.590439000000003</v>
       </c>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="30"/>
       <c r="AK6" s="9"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
         <v>35</v>
       </c>
@@ -1486,14 +1483,14 @@
       <c r="AF7" s="30">
         <v>661.83649000000003</v>
       </c>
-      <c r="AG7" s="53">
+      <c r="AG7" s="49">
         <v>0.59765475999999995</v>
       </c>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="30"/>
       <c r="AK7" s="9"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A8" s="12">
         <v>36</v>
       </c>
@@ -1580,16 +1577,16 @@
       <c r="AF8" s="31">
         <v>50834.453000000001</v>
       </c>
-      <c r="AG8" s="54">
+      <c r="AG8" s="50">
         <v>26.881209999999999</v>
       </c>
       <c r="AI8" s="13"/>
       <c r="AJ8" s="31"/>
       <c r="AK8" s="14"/>
     </row>
-    <row r="9" spans="1:37" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
-        <v>51</v>
+    <row r="9" spans="1:37" s="47" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="33">
+        <v>39</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>14</v>
@@ -1674,14 +1671,14 @@
       <c r="AF9" s="39">
         <v>113285.03</v>
       </c>
-      <c r="AG9" s="55">
+      <c r="AG9" s="51">
         <v>0.51816945999999997</v>
       </c>
       <c r="AI9" s="38"/>
       <c r="AJ9" s="39"/>
       <c r="AK9" s="40"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
         <v>40</v>
       </c>
@@ -1768,14 +1765,14 @@
       <c r="AF10" s="30">
         <v>90419.406000000003</v>
       </c>
-      <c r="AG10" s="53">
+      <c r="AG10" s="49">
         <v>25.967358000000001</v>
       </c>
       <c r="AI10" s="8"/>
       <c r="AJ10" s="30"/>
       <c r="AK10" s="9"/>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>41</v>
       </c>
@@ -1862,14 +1859,14 @@
       <c r="AF11" s="30">
         <v>173699.69</v>
       </c>
-      <c r="AG11" s="53">
+      <c r="AG11" s="49">
         <v>14.811400000000001</v>
       </c>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="30"/>
       <c r="AK11" s="9"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
         <v>42</v>
       </c>
@@ -1956,14 +1953,14 @@
       <c r="AF12" s="30">
         <v>268783.63</v>
       </c>
-      <c r="AG12" s="53">
+      <c r="AG12" s="49">
         <v>2.5109107000000002</v>
       </c>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="30"/>
       <c r="AK12" s="9"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A13" s="7">
         <v>43</v>
       </c>
@@ -2050,14 +2047,14 @@
       <c r="AF13" s="30">
         <v>202102.22</v>
       </c>
-      <c r="AG13" s="53">
+      <c r="AG13" s="49">
         <v>31.597963</v>
       </c>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="30"/>
       <c r="AK13" s="9"/>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
         <v>45</v>
       </c>
@@ -2144,14 +2141,14 @@
       <c r="AF14" s="30">
         <v>175107.88</v>
       </c>
-      <c r="AG14" s="53">
+      <c r="AG14" s="49">
         <v>4.7627664000000003</v>
       </c>
       <c r="AI14" s="8"/>
       <c r="AJ14" s="30"/>
       <c r="AK14" s="9"/>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2163,67 +2160,67 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.15">
       <c r="W16" s="37" t="s">
         <v>48</v>
       </c>
       <c r="X16" s="37"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="7"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="7"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="7"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="7"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="7"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="7"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="7"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="7"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="7"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="7"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="7"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="7"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="7"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="7"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33" s="7"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34" s="7"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35" s="7"/>
     </row>
   </sheetData>
@@ -2242,7 +2239,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E90116-FC9E-D842-BCD3-EA151CFFD05F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
